--- a/Assignments/Literature Review/Literature_Review_Tagged.xlsx
+++ b/Assignments/Literature Review/Literature_Review_Tagged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dda6a6cd85e59f59/University/Research year/polarizer-ring-studies/Assignments/Literature Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_452FD467E2B0D8A58BF0654B78BF0B309E946E89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14E31CF7-26D4-534D-ADE2-B7CE8AE7FFD2}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_452FD467E2B0D8A58BF0654B78BF0B309E946E89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7431BA9-676D-C943-8051-9F4EE177856E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tagged Bibliography" sheetId="1" r:id="rId1"/>
@@ -1246,7 +1246,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1283,6 +1283,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF164E7"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1311,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1342,6 +1348,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1416,6 +1428,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFF164E7"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3023,22 +3038,22 @@
       <c r="H1" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="12" t="s">
         <v>300</v>
       </c>
       <c r="O1" s="4" t="s">
@@ -3100,7 +3115,7 @@
       <c r="A2" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -3148,7 +3163,7 @@
       <c r="A3" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="8"/>
@@ -3198,7 +3213,7 @@
       <c r="A4" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="8"/>
@@ -3242,7 +3257,7 @@
       <c r="A5" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -3294,7 +3309,7 @@
       <c r="A6" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C6" s="8"/>
@@ -3344,7 +3359,7 @@
       <c r="A7" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="8"/>
@@ -3390,7 +3405,7 @@
       <c r="A8" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="8"/>
@@ -3434,7 +3449,7 @@
       <c r="A9" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="8"/>
@@ -3572,7 +3587,7 @@
       <c r="A12" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>102</v>
       </c>
       <c r="C12" s="8"/>
@@ -3620,7 +3635,7 @@
       <c r="A13" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -3664,7 +3679,7 @@
       <c r="A14" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>113</v>
       </c>
       <c r="C14" s="8"/>
@@ -3714,7 +3729,7 @@
       <c r="A15" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>121</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -3760,7 +3775,7 @@
       <c r="A16" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>126</v>
       </c>
       <c r="C16" s="8"/>
@@ -3890,7 +3905,7 @@
       <c r="A19" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>149</v>
       </c>
       <c r="C19" s="8"/>
@@ -3936,7 +3951,7 @@
       <c r="A20" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="10" t="s">
         <v>155</v>
       </c>
       <c r="C20" s="8"/>
@@ -3988,7 +4003,7 @@
       <c r="A21" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>161</v>
       </c>
       <c r="C21" s="8"/>
@@ -4038,7 +4053,7 @@
       <c r="A22" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="10" t="s">
         <v>169</v>
       </c>
       <c r="C22" s="8"/>
@@ -4128,7 +4143,7 @@
       <c r="A24" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="10" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="8"/>
@@ -4178,7 +4193,7 @@
       <c r="A25" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>193</v>
       </c>
       <c r="C25" s="8"/>
@@ -4224,7 +4239,7 @@
       <c r="A26" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="10" t="s">
         <v>199</v>
       </c>
       <c r="C26" s="8"/>
@@ -4314,7 +4329,7 @@
       <c r="A28" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="10" t="s">
         <v>211</v>
       </c>
       <c r="C28" s="8"/>
@@ -4358,7 +4373,7 @@
       <c r="A29" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="10" t="s">
         <v>218</v>
       </c>
       <c r="C29" s="8"/>
@@ -4402,7 +4417,7 @@
       <c r="A30" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="10" t="s">
         <v>225</v>
       </c>
       <c r="C30" s="8"/>
@@ -4578,7 +4593,7 @@
       <c r="A34" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="10" t="s">
         <v>252</v>
       </c>
       <c r="C34" s="8"/>
@@ -4624,7 +4639,7 @@
       <c r="A35" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="10" t="s">
         <v>260</v>
       </c>
       <c r="C35" s="8"/>
